--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113439236</v>
+        <v>113439218</v>
       </c>
       <c r="B2" t="n">
-        <v>97215</v>
+        <v>78121</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754777</v>
+        <v>754702</v>
       </c>
       <c r="R2" t="n">
-        <v>7170150</v>
+        <v>7170134</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113439218</v>
+        <v>113439236</v>
       </c>
       <c r="B3" t="n">
-        <v>78105</v>
+        <v>97231</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754702</v>
+        <v>754777</v>
       </c>
       <c r="R3" t="n">
-        <v>7170134</v>
+        <v>7170150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113439218</v>
       </c>
       <c r="B2" t="n">
-        <v>78121</v>
+        <v>78133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>113439236</v>
       </c>
       <c r="B3" t="n">
-        <v>97231</v>
+        <v>97243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113439218</v>
+        <v>113439236</v>
       </c>
       <c r="B2" t="n">
-        <v>78133</v>
+        <v>97243</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754702</v>
+        <v>754777</v>
       </c>
       <c r="R2" t="n">
-        <v>7170134</v>
+        <v>7170150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113439236</v>
+        <v>113439218</v>
       </c>
       <c r="B3" t="n">
-        <v>97243</v>
+        <v>78133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754777</v>
+        <v>754702</v>
       </c>
       <c r="R3" t="n">
-        <v>7170150</v>
+        <v>7170134</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113439236</v>
       </c>
       <c r="B2" t="n">
-        <v>97243</v>
+        <v>97265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>113439218</v>
       </c>
       <c r="B3" t="n">
-        <v>78133</v>
+        <v>78155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113439236</v>
       </c>
       <c r="B2" t="n">
-        <v>97265</v>
+        <v>97269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>113439218</v>
       </c>
       <c r="B3" t="n">
-        <v>78155</v>
+        <v>78158</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113439236</v>
       </c>
       <c r="B2" t="n">
-        <v>97269</v>
+        <v>97275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>113439218</v>
       </c>
       <c r="B3" t="n">
-        <v>78158</v>
+        <v>78164</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113439236</v>
+        <v>113439218</v>
       </c>
       <c r="B2" t="n">
-        <v>97275</v>
+        <v>78164</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754777</v>
+        <v>754702</v>
       </c>
       <c r="R2" t="n">
-        <v>7170150</v>
+        <v>7170134</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113439218</v>
+        <v>113439236</v>
       </c>
       <c r="B3" t="n">
-        <v>78164</v>
+        <v>97275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754702</v>
+        <v>754777</v>
       </c>
       <c r="R3" t="n">
-        <v>7170134</v>
+        <v>7170150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113439218</v>
+        <v>113439236</v>
       </c>
       <c r="B2" t="n">
-        <v>78164</v>
+        <v>97282</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754702</v>
+        <v>754777</v>
       </c>
       <c r="R2" t="n">
-        <v>7170134</v>
+        <v>7170150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113439236</v>
+        <v>113439218</v>
       </c>
       <c r="B3" t="n">
-        <v>97275</v>
+        <v>78171</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754777</v>
+        <v>754702</v>
       </c>
       <c r="R3" t="n">
-        <v>7170150</v>
+        <v>7170134</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113439236</v>
+        <v>113439218</v>
       </c>
       <c r="B2" t="n">
-        <v>97282</v>
+        <v>78173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754777</v>
+        <v>754702</v>
       </c>
       <c r="R2" t="n">
-        <v>7170150</v>
+        <v>7170134</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113439218</v>
+        <v>113439236</v>
       </c>
       <c r="B3" t="n">
-        <v>78171</v>
+        <v>97287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754702</v>
+        <v>754777</v>
       </c>
       <c r="R3" t="n">
-        <v>7170134</v>
+        <v>7170150</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113439218</v>
       </c>
       <c r="B2" t="n">
-        <v>78173</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>113439236</v>
       </c>
       <c r="B3" t="n">
-        <v>97287</v>
+        <v>97315</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113439218</v>
+        <v>113439236</v>
       </c>
       <c r="B2" t="n">
-        <v>78201</v>
+        <v>97315</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>754702</v>
+        <v>754777</v>
       </c>
       <c r="R2" t="n">
-        <v>7170134</v>
+        <v>7170150</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113439236</v>
+        <v>113439218</v>
       </c>
       <c r="B3" t="n">
-        <v>97315</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>754777</v>
+        <v>754702</v>
       </c>
       <c r="R3" t="n">
-        <v>7170150</v>
+        <v>7170134</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113439236</v>
       </c>
       <c r="B2" t="n">
-        <v>97315</v>
+        <v>97319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 68169-2020 artfynd.xlsx
+++ b/artfynd/A 68169-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
